--- a/artifacts/YUNZ-20/selftest/stage7/browser/蓉城战役日报-20261014.xlsx
+++ b/artifacts/YUNZ-20/selftest/stage7/browser/蓉城战役日报-20261014.xlsx
@@ -583,7 +583,7 @@
         <v>日报自测：等待外部依赖</v>
       </c>
       <c r="I2" t="str">
-        <v>2026-10-14 20:18:54</v>
+        <v>2026-10-14 20:35:49</v>
       </c>
       <c r="J2" t="str">
         <v>项目负责人</v>
@@ -615,7 +615,7 @@
         <v>被阻塞</v>
       </c>
       <c r="I3" t="str">
-        <v>2026-10-14 20:18:54</v>
+        <v>2026-10-14 20:35:49</v>
       </c>
       <c r="J3" t="str">
         <v>项目负责人</v>
@@ -647,7 +647,7 @@
         <v>已延期</v>
       </c>
       <c r="I4" t="str">
-        <v>2026-10-14 20:18:54</v>
+        <v>2026-10-14 20:35:49</v>
       </c>
       <c r="J4" t="str">
         <v>项目负责人</v>
@@ -679,7 +679,7 @@
         <v>进行中</v>
       </c>
       <c r="I5" t="str">
-        <v>2026-10-14 20:18:54</v>
+        <v>2026-10-14 20:35:49</v>
       </c>
       <c r="J5" t="str">
         <v>项目负责人</v>
